--- a/parameters/UA/ammonia/pipeline_parameters.xlsx
+++ b/parameters/UA/ammonia/pipeline_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samiyhanaqvi/Desktop/SHIELD/updating-main/Geo-X/parameters/NA/ammonia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B17424-E50A-E248-8770-6073D6E05FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19693762-8E47-4231-8E13-282369DE3BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9980" yWindow="740" windowWidth="19420" windowHeight="17360" xr2:uid="{94028C1A-34CC-4B53-868B-8FD234C28ADF}"/>
+    <workbookView xWindow="3630" yWindow="4350" windowWidth="16770" windowHeight="9330" activeTab="3" xr2:uid="{94028C1A-34CC-4B53-868B-8FD234C28ADF}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -508,26 +508,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0432B26-F3F0-43E1-A0D6-6197719E0B28}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -535,7 +535,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -543,7 +543,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -551,7 +551,7 @@
         <v>6.1381900000000004E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -559,7 +559,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -567,7 +567,7 @@
         <v>8262000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -575,7 +575,7 @@
         <v>1775000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -591,17 +591,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3769E0-8D26-4542-AE82-68EE05500E52}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -609,7 +609,7 @@
         <v>36.432234259545197</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -625,17 +625,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0FBB5F-3E9B-4EE5-99BF-10A517EB976F}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -643,7 +643,7 @@
         <v>57.588615193195757</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -659,17 +659,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13374701-BB04-4EB3-9B4E-2501A6D51514}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -677,7 +677,7 @@
         <v>79.478855072970205</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
